--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.96015143516355</v>
+        <v>5.681024608214076</v>
       </c>
       <c r="D2" t="n">
-        <v>34.94769902063676</v>
+        <v>5.679001090853474</v>
       </c>
       <c r="E2" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F2" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.02092615989763</v>
+        <v>3.903400500983365</v>
       </c>
       <c r="D3" t="n">
-        <v>24.15656832352442</v>
+        <v>3.925442352572718</v>
       </c>
       <c r="E3" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F3" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.20576651517059</v>
+        <v>4.908437058715222</v>
       </c>
       <c r="D4" t="n">
-        <v>29.94868502194773</v>
+        <v>4.866661316066507</v>
       </c>
       <c r="E4" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F4" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.04076420666262</v>
+        <v>2.769124183582676</v>
       </c>
       <c r="D5" t="n">
-        <v>17.31579044167384</v>
+        <v>2.813815946771999</v>
       </c>
       <c r="E5" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F5" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.23501194731082</v>
+        <v>4.750689441438009</v>
       </c>
       <c r="D6" t="n">
-        <v>28.79288168080658</v>
+        <v>4.67884327313107</v>
       </c>
       <c r="E6" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F6" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.34823041891458</v>
+        <v>5.256587443073618</v>
       </c>
       <c r="D7" t="n">
-        <v>32.32626291403159</v>
+        <v>5.253017723530133</v>
       </c>
       <c r="E7" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F7" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.44354635528044</v>
+        <v>4.784576282733072</v>
       </c>
       <c r="D8" t="n">
-        <v>29.06904016688737</v>
+        <v>4.723719027119197</v>
       </c>
       <c r="E8" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F8" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.9205449856571</v>
+        <v>2.912088560169279</v>
       </c>
       <c r="D9" t="n">
-        <v>18.3572300994664</v>
+        <v>2.983049891163289</v>
       </c>
       <c r="E9" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F9" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.46333021729569</v>
+        <v>3.97529116031055</v>
       </c>
       <c r="D10" t="n">
-        <v>24.75135525086803</v>
+        <v>4.022095228266056</v>
       </c>
       <c r="E10" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F10" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.17998880374925</v>
+        <v>4.091748180609254</v>
       </c>
       <c r="D11" t="n">
-        <v>24.76684374935742</v>
+        <v>4.024612109270581</v>
       </c>
       <c r="E11" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F11" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.97121849391666</v>
+        <v>6.495323005261457</v>
       </c>
       <c r="D12" t="n">
-        <v>39.57256920059736</v>
+        <v>6.430542495097071</v>
       </c>
       <c r="E12" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F12" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>61.19366496561226</v>
+        <v>9.943970556911992</v>
       </c>
       <c r="D13" t="n">
-        <v>61.37833429258288</v>
+        <v>9.973979322544718</v>
       </c>
       <c r="E13" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F13" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>67.85846911239085</v>
+        <v>11.02700123076351</v>
       </c>
       <c r="D14" t="n">
-        <v>68.04495320947889</v>
+        <v>11.05730489654032</v>
       </c>
       <c r="E14" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F14" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.15223356324128</v>
+        <v>2.787237954026708</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84474964733029</v>
+        <v>2.737271817691173</v>
       </c>
       <c r="E15" t="n">
-        <v>14.72783844127375</v>
+        <v>2.393273746706984</v>
       </c>
       <c r="F15" t="n">
-        <v>14.75754764391609</v>
+        <v>2.398101492136364</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
